--- a/JsonConverter/ExcelFiles/Furniture.xlsx
+++ b/JsonConverter/ExcelFiles/Furniture.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18948" windowHeight="6360" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="11316" windowHeight="6288" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,7 +19,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+  <x:si>
+    <x:t>Table</x:t>
+  </x:si>
   <x:si>
     <x:t>맥주 빨리 먹기 대회' 라고 적혀 있다.</x:t>
   </x:si>
@@ -27,127 +30,133 @@
     <x:t>어떤 피부도 화사하게 비춰주는 인플루언서용 조명.</x:t>
   </x:si>
   <x:si>
+    <x:t>햇빛이 부족한 실내에서도 잘 자라는 재배기.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 OTT 이용이 가능하며 오롯이 자신만의 세계에 빠져들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>책은 단 한 권만 읽은 사람이 가장 무섭다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜딩 포즈 점검에 안성맞춤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InstallPointId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FurnitureName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멀리 보는 연습을 하면 좋은 시력이 유지된다는 이야기가 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설치포인트ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HeroId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전신 거울</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀카조명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가구 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가구 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풍경 그림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Price</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유머모음집</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>식물재배기</x:t>
   </x:si>
   <x:si>
-    <x:t>furniture_01</x:t>
+    <x:t>hero_06</x:t>
   </x:si>
   <x:si>
     <x:t>트로피</x:t>
   </x:si>
   <x:si>
-    <x:t>햇빛이 부족한 실내에서도 잘 자라는 재배기.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀카조명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전신 거울</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FurnitureName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>InstallPointId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Price</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가구 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HeroId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가구 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>책은 단 한 권만 읽은 사람이 가장 무섭다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유머모음집</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설치포인트ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모든 OTT 이용이 가능하며 오롯이 자신만의 세계에 빠져들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풍경 그림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멀리 보는 연습을 하면 좋은 시력이 유지된다는 이야기가 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜딩 포즈 점검에 안성맞춤.</x:t>
+    <x:t>Stand</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wall</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -193,66 +202,21 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="&quot;맑은 고딕&quot;"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff008000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="&quot;맑은 고딕&quot;"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff008000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="&quot;맑은 고딕&quot;"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="&quot;맑은 고딕&quot;"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Times New Roman"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Times New Roman"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff008000"/>
+    </x:font>
+    <x:font>
+      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff008000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Times New Roman"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff008000"/>
+    </x:font>
   </x:fonts>
   <x:fills count="4">
     <x:fill>
@@ -944,62 +908,62 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D2" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
@@ -1016,132 +980,146 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="3">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="F4" s="3"/>
+      <x:c r="F4" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="3">
         <x:v>900</x:v>
       </x:c>
-      <x:c r="F5" s="3"/>
+      <x:c r="F5" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E6" s="3">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="F6" s="3"/>
+      <x:c r="F6" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="3">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="F7" s="3"/>
+      <x:c r="F7" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G7" s="10"/>
     </x:row>
     <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="3">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="F8" s="3"/>
+      <x:c r="F8" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G8" s="10"/>
     </x:row>
     <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="3">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="F9" s="3"/>
+      <x:c r="F9" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G9" s="10"/>
     </x:row>
     <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A10" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E10" s="3">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="F10" s="3"/>
+      <x:c r="F10" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G10" s="10"/>
     </x:row>
     <x:row r="11" spans="1:7" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Furniture.xlsx
+++ b/JsonConverter/ExcelFiles/Furniture.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="11316" windowHeight="6288" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,142 +21,142 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <x:si>
+    <x:t>모든 OTT 이용이 가능하며 오롯이 자신만의 세계에 빠져들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤 피부도 화사하게 비춰주는 인플루언서용 조명.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햇빛이 부족한 실내에서도 잘 자라는 재배기.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wall</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가구 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풍경 그림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물재배기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설치포인트ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀카조명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HeroId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stand</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가구 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>Table</x:t>
   </x:si>
   <x:si>
+    <x:t>hero_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전신 거울</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유머모음집</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Price</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>맥주 빨리 먹기 대회' 라고 적혀 있다.</x:t>
   </x:si>
   <x:si>
-    <x:t>어떤 피부도 화사하게 비춰주는 인플루언서용 조명.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햇빛이 부족한 실내에서도 잘 자라는 재배기.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모든 OTT 이용이 가능하며 오롯이 자신만의 세계에 빠져들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>책은 단 한 권만 읽은 사람이 가장 무섭다...</x:t>
+    <x:t>어떤 분야든 책을 단 한 권만 읽은 사람이 가장 무섭다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멀리 보는 연습을 하면 좋은 시력이 유지된다는 이야기가 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>furniture_03</x:t>
   </x:si>
   <x:si>
+    <x:t>InstallPointId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜딩 포즈 점검에 안성맞춤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>furniture_05</x:t>
+  </x:si>
+  <x:si>
     <x:t>furniture_01</x:t>
   </x:si>
   <x:si>
-    <x:t>랜딩 포즈 점검에 안성맞춤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_05</x:t>
+    <x:t>FurnitureName</x:t>
   </x:si>
   <x:si>
     <x:t>furniture_04</x:t>
   </x:si>
   <x:si>
-    <x:t>InstallPointId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>furniture_06</x:t>
-  </x:si>
-  <x:si>
     <x:t>furniture_02</x:t>
   </x:si>
   <x:si>
-    <x:t>FurnitureName</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>트로피</x:t>
   </x:si>
   <x:si>
     <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>가격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멀리 보는 연습을 하면 좋은 시력이 유지된다는 이야기가 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설치포인트ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HeroId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전신 거울</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀카조명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가구 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가구 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풍경 그림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Price</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유머모음집</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물재배기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>트로피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stand</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wall</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -908,62 +908,62 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D2" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
@@ -980,145 +980,145 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="3">
-        <x:v>1000</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="3">
-        <x:v>900</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="3">
-        <x:v>800</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="3">
-        <x:v>700</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G7" s="10"/>
     </x:row>
     <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="3">
-        <x:v>600</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G8" s="10"/>
     </x:row>
     <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="3">
-        <x:v>500</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G9" s="10"/>
     </x:row>
     <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A10" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E10" s="3">
-        <x:v>400</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="10"/>
     </x:row>
